--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -1410,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113014401</v>
+        <v>113015164</v>
       </c>
       <c r="B9" t="n">
-        <v>90049</v>
+        <v>5478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,35 +1426,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561271</v>
+        <v>561290</v>
       </c>
       <c r="R9" t="n">
-        <v>6585823</v>
+        <v>6585993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113014936</v>
+        <v>113014401</v>
       </c>
       <c r="B10" t="n">
-        <v>97298</v>
+        <v>90049</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,37 +1530,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1563,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561307</v>
+        <v>561271</v>
       </c>
       <c r="R10" t="n">
-        <v>6585872</v>
+        <v>6585823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113015164</v>
+        <v>113014936</v>
       </c>
       <c r="B11" t="n">
-        <v>5478</v>
+        <v>97298</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,44 +1633,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561290</v>
+        <v>561307</v>
       </c>
       <c r="R11" t="n">
-        <v>6585993</v>
+        <v>6585872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427513</v>
+        <v>113426721</v>
       </c>
       <c r="B41" t="n">
         <v>90049</v>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561256</v>
+        <v>561083</v>
       </c>
       <c r="R41" t="n">
-        <v>6585858</v>
+        <v>6586092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113426721</v>
+        <v>113427513</v>
       </c>
       <c r="B42" t="n">
         <v>90049</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561083</v>
+        <v>561256</v>
       </c>
       <c r="R42" t="n">
-        <v>6586092</v>
+        <v>6585858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113015378</v>
+        <v>113014423</v>
       </c>
       <c r="B2" t="n">
-        <v>91313</v>
+        <v>91306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561218</v>
+        <v>561279</v>
       </c>
       <c r="R2" t="n">
-        <v>6586077</v>
+        <v>6585820</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113015366</v>
+        <v>113014243</v>
       </c>
       <c r="B3" t="n">
-        <v>97298</v>
+        <v>90065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,37 +790,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561220</v>
+        <v>561231</v>
       </c>
       <c r="R3" t="n">
-        <v>6586054</v>
+        <v>6585841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113015193</v>
+        <v>113014867</v>
       </c>
       <c r="B4" t="n">
-        <v>91313</v>
+        <v>91329</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561311</v>
+        <v>561305</v>
       </c>
       <c r="R4" t="n">
-        <v>6586024</v>
+        <v>6585865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113014310</v>
+        <v>113015404</v>
       </c>
       <c r="B5" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561243</v>
+        <v>561188</v>
       </c>
       <c r="R5" t="n">
-        <v>6585835</v>
+        <v>6586093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113015273</v>
+        <v>113015388</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>97314</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,44 +1099,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561359</v>
+        <v>561206</v>
       </c>
       <c r="R6" t="n">
-        <v>6585999</v>
+        <v>6586097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113015404</v>
+        <v>113014306</v>
       </c>
       <c r="B7" t="n">
-        <v>90049</v>
+        <v>89127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561188</v>
+        <v>561231</v>
       </c>
       <c r="R7" t="n">
-        <v>6586093</v>
+        <v>6585833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113014229</v>
+        <v>113015465</v>
       </c>
       <c r="B8" t="n">
-        <v>90049</v>
+        <v>97314</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,28 +1314,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561227</v>
+        <v>561195</v>
       </c>
       <c r="R8" t="n">
-        <v>6585824</v>
+        <v>6586091</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113015164</v>
+        <v>113015366</v>
       </c>
       <c r="B9" t="n">
-        <v>5478</v>
+        <v>97314</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,44 +1426,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561290</v>
+        <v>561220</v>
       </c>
       <c r="R9" t="n">
-        <v>6585993</v>
+        <v>6586054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1529,7 @@
         <v>113014401</v>
       </c>
       <c r="B10" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113014936</v>
+        <v>113013830</v>
       </c>
       <c r="B11" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,7 +1664,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1671,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561307</v>
+        <v>561153</v>
       </c>
       <c r="R11" t="n">
-        <v>6585872</v>
+        <v>6585854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113014243</v>
+        <v>113014310</v>
       </c>
       <c r="B12" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561231</v>
+        <v>561243</v>
       </c>
       <c r="R12" t="n">
-        <v>6585841</v>
+        <v>6585835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113015092</v>
+        <v>113013673</v>
       </c>
       <c r="B13" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,16 +1877,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561272</v>
+        <v>561203</v>
       </c>
       <c r="R13" t="n">
-        <v>6585900</v>
+        <v>6586017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113015388</v>
+        <v>113015273</v>
       </c>
       <c r="B14" t="n">
-        <v>97298</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,48 +1959,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561206</v>
+        <v>561359</v>
       </c>
       <c r="R14" t="n">
-        <v>6586097</v>
+        <v>6585999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113014423</v>
+        <v>113013923</v>
       </c>
       <c r="B15" t="n">
-        <v>91290</v>
+        <v>91329</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561279</v>
+        <v>561174</v>
       </c>
       <c r="R15" t="n">
-        <v>6585820</v>
+        <v>6585809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113015292</v>
+        <v>113014936</v>
       </c>
       <c r="B16" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2213,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561312</v>
+        <v>561307</v>
       </c>
       <c r="R16" t="n">
-        <v>6586022</v>
+        <v>6585872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113014306</v>
+        <v>113013600</v>
       </c>
       <c r="B17" t="n">
-        <v>89111</v>
+        <v>90065</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,35 +2286,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Malmtorp (Malmtorp), Srm</t>
+          <t>Johannesberg (Johannesberg), Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561231</v>
+        <v>561117</v>
       </c>
       <c r="R17" t="n">
-        <v>6585833</v>
+        <v>6586128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113013726</v>
+        <v>113015193</v>
       </c>
       <c r="B18" t="n">
-        <v>97298</v>
+        <v>91329</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2390,37 +2385,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2428,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561223</v>
+        <v>561311</v>
       </c>
       <c r="R18" t="n">
-        <v>6586010</v>
+        <v>6586024</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113015465</v>
+        <v>113014334</v>
       </c>
       <c r="B19" t="n">
-        <v>97298</v>
+        <v>91329</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,37 +2488,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2540,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561195</v>
+        <v>561255</v>
       </c>
       <c r="R19" t="n">
-        <v>6586091</v>
+        <v>6585842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113013830</v>
+        <v>113015292</v>
       </c>
       <c r="B20" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,7 +2614,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2652,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561153</v>
+        <v>561312</v>
       </c>
       <c r="R20" t="n">
-        <v>6585854</v>
+        <v>6586022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113013598</v>
+        <v>113013627</v>
       </c>
       <c r="B21" t="n">
-        <v>90426</v>
+        <v>90029</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,35 +2707,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>4660</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Johannesberg (Johannesberg), Srm</t>
+          <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561117</v>
+        <v>561122</v>
       </c>
       <c r="R21" t="n">
-        <v>6586128</v>
+        <v>6586060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,10 +2794,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113015468</v>
+        <v>113014229</v>
       </c>
       <c r="B22" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561187</v>
+        <v>561227</v>
       </c>
       <c r="R22" t="n">
-        <v>6586104</v>
+        <v>6585824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2920,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113014568</v>
+        <v>113015164</v>
       </c>
       <c r="B23" t="n">
-        <v>91306</v>
+        <v>5478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,35 +2913,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>101410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561287</v>
+        <v>561290</v>
       </c>
       <c r="R23" t="n">
-        <v>6585833</v>
+        <v>6585993</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113014867</v>
+        <v>113014568</v>
       </c>
       <c r="B24" t="n">
-        <v>91313</v>
+        <v>91322</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3046,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561305</v>
+        <v>561287</v>
       </c>
       <c r="R24" t="n">
-        <v>6585865</v>
+        <v>6585833</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,10 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113013600</v>
+        <v>113014728</v>
       </c>
       <c r="B25" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,14 +3145,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Johannesberg (Johannesberg), Srm</t>
+          <t>Malmtorp (Malmtorp), Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561117</v>
+        <v>561296</v>
       </c>
       <c r="R25" t="n">
-        <v>6586128</v>
+        <v>6585847</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113014060</v>
+        <v>113015468</v>
       </c>
       <c r="B26" t="n">
-        <v>91313</v>
+        <v>90065</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3245,21 +3227,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3252,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561222</v>
+        <v>561187</v>
       </c>
       <c r="R26" t="n">
-        <v>6585792</v>
+        <v>6586104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,10 +3314,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113014728</v>
+        <v>113013598</v>
       </c>
       <c r="B27" t="n">
-        <v>90049</v>
+        <v>90442</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3344,39 +3326,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Malmtorp (Malmtorp), Srm</t>
+          <t>Johannesberg (Johannesberg), Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561296</v>
+        <v>561117</v>
       </c>
       <c r="R27" t="n">
-        <v>6585847</v>
+        <v>6586128</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113013923</v>
+        <v>113015092</v>
       </c>
       <c r="B28" t="n">
-        <v>91313</v>
+        <v>97314</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,28 +3429,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3476,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561174</v>
+        <v>561272</v>
       </c>
       <c r="R28" t="n">
-        <v>6585809</v>
+        <v>6585900</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113014718</v>
+        <v>113014647</v>
       </c>
       <c r="B29" t="n">
-        <v>91313</v>
+        <v>90065</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561293</v>
+        <v>561292</v>
       </c>
       <c r="R29" t="n">
-        <v>6585835</v>
+        <v>6585839</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113014647</v>
+        <v>113013726</v>
       </c>
       <c r="B30" t="n">
-        <v>90049</v>
+        <v>97314</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3653,28 +3644,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561292</v>
+        <v>561223</v>
       </c>
       <c r="R30" t="n">
-        <v>6585839</v>
+        <v>6586010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113013673</v>
+        <v>113014060</v>
       </c>
       <c r="B31" t="n">
-        <v>97298</v>
+        <v>91329</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561203</v>
+        <v>561222</v>
       </c>
       <c r="R31" t="n">
-        <v>6586017</v>
+        <v>6585792</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113013627</v>
+        <v>113014718</v>
       </c>
       <c r="B32" t="n">
-        <v>90013</v>
+        <v>91329</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4660</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561122</v>
+        <v>561293</v>
       </c>
       <c r="R32" t="n">
-        <v>6586060</v>
+        <v>6585835</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113014334</v>
+        <v>113015378</v>
       </c>
       <c r="B33" t="n">
-        <v>91313</v>
+        <v>91329</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561255</v>
+        <v>561218</v>
       </c>
       <c r="R33" t="n">
-        <v>6585842</v>
+        <v>6586077</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
         <v>113384128</v>
       </c>
       <c r="B34" t="n">
-        <v>91313</v>
+        <v>91329</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>113397423</v>
       </c>
       <c r="B35" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>113415824</v>
       </c>
       <c r="B36" t="n">
-        <v>91282</v>
+        <v>91298</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427412</v>
+        <v>113427121</v>
       </c>
       <c r="B37" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561202</v>
+        <v>561215</v>
       </c>
       <c r="R37" t="n">
-        <v>6586118</v>
+        <v>6585917</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
         <v>113427186</v>
       </c>
       <c r="B38" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427169</v>
+        <v>113430772</v>
       </c>
       <c r="B39" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561230</v>
+        <v>561351</v>
       </c>
       <c r="R39" t="n">
-        <v>6585884</v>
+        <v>6586008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427121</v>
+        <v>113427169</v>
       </c>
       <c r="B40" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561215</v>
+        <v>561230</v>
       </c>
       <c r="R40" t="n">
-        <v>6585917</v>
+        <v>6585884</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113426721</v>
+        <v>113427513</v>
       </c>
       <c r="B41" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561083</v>
+        <v>561256</v>
       </c>
       <c r="R41" t="n">
-        <v>6586092</v>
+        <v>6585858</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427513</v>
+        <v>113427412</v>
       </c>
       <c r="B42" t="n">
-        <v>90049</v>
+        <v>90065</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561256</v>
+        <v>561202</v>
       </c>
       <c r="R42" t="n">
-        <v>6585858</v>
+        <v>6586118</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,10 +5004,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113430910</v>
+        <v>113426721</v>
       </c>
       <c r="B43" t="n">
-        <v>56781</v>
+        <v>90065</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5020,27 +5020,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5048,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>561252</v>
+        <v>561083</v>
       </c>
       <c r="R43" t="n">
-        <v>6586009</v>
+        <v>6586092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5092,6 +5091,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5107,6 +5107,430 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>113430910</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56781</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>561252</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6586009</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>113444155</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90433</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>561162</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6586134</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>113448130</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90661</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>561087</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6586050</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>113444211</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56781</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>561306</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6585836</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -5216,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113444155</v>
+        <v>113448130</v>
       </c>
       <c r="B45" t="n">
-        <v>90433</v>
+        <v>90661</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5232,21 +5232,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4217</v>
+        <v>6031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5259,13 +5259,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>561162</v>
+        <v>561087</v>
       </c>
       <c r="R45" t="n">
-        <v>6586134</v>
+        <v>6586050</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113448130</v>
+        <v>113444211</v>
       </c>
       <c r="B46" t="n">
-        <v>90661</v>
+        <v>56781</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,30 +5334,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5365,13 +5366,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561087</v>
+        <v>561306</v>
       </c>
       <c r="R46" t="n">
-        <v>6586050</v>
+        <v>6585836</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5395,12 +5396,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5409,7 +5410,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113444211</v>
+        <v>113444155</v>
       </c>
       <c r="B47" t="n">
-        <v>56781</v>
+        <v>90433</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,31 +5440,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5472,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561306</v>
+        <v>561162</v>
       </c>
       <c r="R47" t="n">
-        <v>6585836</v>
+        <v>6586134</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5516,6 +5515,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B34" t="n">
-        <v>91329</v>
+        <v>90065</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,35 +4069,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R34" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,6 +4140,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4156,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B35" t="n">
-        <v>90065</v>
+        <v>91329</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,37 +4175,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R35" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,7 +4244,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427121</v>
+        <v>113427412</v>
       </c>
       <c r="B37" t="n">
         <v>90065</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561215</v>
+        <v>561202</v>
       </c>
       <c r="R37" t="n">
-        <v>6585917</v>
+        <v>6586118</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113430772</v>
+        <v>113426721</v>
       </c>
       <c r="B39" t="n">
         <v>90065</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561351</v>
+        <v>561083</v>
       </c>
       <c r="R39" t="n">
-        <v>6586008</v>
+        <v>6586092</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427169</v>
+        <v>113430772</v>
       </c>
       <c r="B40" t="n">
         <v>90065</v>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561230</v>
+        <v>561351</v>
       </c>
       <c r="R40" t="n">
-        <v>6585884</v>
+        <v>6586008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B42" t="n">
         <v>90065</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R42" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113426721</v>
+        <v>113427121</v>
       </c>
       <c r="B43" t="n">
         <v>90065</v>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>561083</v>
+        <v>561215</v>
       </c>
       <c r="R43" t="n">
-        <v>6586092</v>
+        <v>6585917</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B34" t="n">
-        <v>90065</v>
+        <v>91341</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,37 +4069,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R34" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,7 +4138,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4159,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B35" t="n">
-        <v>91329</v>
+        <v>90077</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,35 +4172,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R35" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,6 +4243,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>113415824</v>
       </c>
       <c r="B36" t="n">
-        <v>91298</v>
+        <v>91310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427412</v>
+        <v>113427513</v>
       </c>
       <c r="B37" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561202</v>
+        <v>561256</v>
       </c>
       <c r="R37" t="n">
-        <v>6586118</v>
+        <v>6585858</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
         <v>113427186</v>
       </c>
       <c r="B38" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113426721</v>
+        <v>113427412</v>
       </c>
       <c r="B39" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561083</v>
+        <v>561202</v>
       </c>
       <c r="R39" t="n">
-        <v>6586092</v>
+        <v>6586118</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113430772</v>
+        <v>113426721</v>
       </c>
       <c r="B40" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561351</v>
+        <v>561083</v>
       </c>
       <c r="R40" t="n">
-        <v>6586008</v>
+        <v>6586092</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427513</v>
+        <v>113430772</v>
       </c>
       <c r="B41" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561256</v>
+        <v>561351</v>
       </c>
       <c r="R41" t="n">
-        <v>6585858</v>
+        <v>6586008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
         <v>113427169</v>
       </c>
       <c r="B42" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>113427121</v>
       </c>
       <c r="B43" t="n">
-        <v>90065</v>
+        <v>90077</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>113430910</v>
       </c>
       <c r="B44" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113448130</v>
       </c>
       <c r="B45" t="n">
-        <v>90661</v>
+        <v>90673</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>113444211</v>
       </c>
       <c r="B46" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>113444155</v>
       </c>
       <c r="B47" t="n">
-        <v>90433</v>
+        <v>90445</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113415824</v>
+        <v>113430772</v>
       </c>
       <c r="B36" t="n">
-        <v>91310</v>
+        <v>90077</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4278,21 +4278,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561276</v>
+        <v>561351</v>
       </c>
       <c r="R36" t="n">
-        <v>6586009</v>
+        <v>6586008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4368,7 +4368,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427513</v>
+        <v>113427121</v>
       </c>
       <c r="B37" t="n">
         <v>90077</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561256</v>
+        <v>561215</v>
       </c>
       <c r="R37" t="n">
-        <v>6585858</v>
+        <v>6585917</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427186</v>
+        <v>113427412</v>
       </c>
       <c r="B38" t="n">
         <v>90077</v>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561348</v>
+        <v>561202</v>
       </c>
       <c r="R38" t="n">
-        <v>6585875</v>
+        <v>6586118</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B39" t="n">
         <v>90077</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R39" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113426721</v>
+        <v>113427186</v>
       </c>
       <c r="B40" t="n">
         <v>90077</v>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561083</v>
+        <v>561348</v>
       </c>
       <c r="R40" t="n">
-        <v>6586092</v>
+        <v>6585875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113430772</v>
+        <v>113426721</v>
       </c>
       <c r="B41" t="n">
         <v>90077</v>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561351</v>
+        <v>561083</v>
       </c>
       <c r="R41" t="n">
-        <v>6586008</v>
+        <v>6586092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427169</v>
+        <v>113427513</v>
       </c>
       <c r="B42" t="n">
         <v>90077</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561230</v>
+        <v>561256</v>
       </c>
       <c r="R42" t="n">
-        <v>6585884</v>
+        <v>6585858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,10 +5004,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113427121</v>
+        <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>90077</v>
+        <v>56782</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5020,26 +5020,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5047,10 +5048,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>561215</v>
+        <v>561252</v>
       </c>
       <c r="R43" t="n">
-        <v>6585917</v>
+        <v>6586009</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5092,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113430910</v>
+        <v>113444211</v>
       </c>
       <c r="B44" t="n">
         <v>56782</v>
@@ -5154,13 +5154,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>561252</v>
+        <v>561306</v>
       </c>
       <c r="R44" t="n">
-        <v>6586009</v>
+        <v>6585836</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113448130</v>
+        <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90673</v>
+        <v>90445</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5232,21 +5232,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6031</v>
+        <v>4217</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5259,13 +5259,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>561087</v>
+        <v>561162</v>
       </c>
       <c r="R45" t="n">
-        <v>6586050</v>
+        <v>6586134</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113444211</v>
+        <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>56782</v>
+        <v>91310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5338,27 +5338,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5366,13 +5365,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561306</v>
+        <v>561276</v>
       </c>
       <c r="R46" t="n">
-        <v>6585836</v>
+        <v>6586009</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5396,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5410,6 +5409,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113444155</v>
+        <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>90445</v>
+        <v>90673</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4217</v>
+        <v>6031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,13 +5471,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561162</v>
+        <v>561087</v>
       </c>
       <c r="R47" t="n">
-        <v>6586134</v>
+        <v>6586050</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B34" t="n">
-        <v>91341</v>
+        <v>90099</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,35 +4069,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R34" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,6 +4140,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4156,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B35" t="n">
-        <v>90077</v>
+        <v>91363</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,37 +4175,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R35" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,7 +4244,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>113430772</v>
       </c>
       <c r="B36" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427121</v>
+        <v>113427186</v>
       </c>
       <c r="B37" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561215</v>
+        <v>561348</v>
       </c>
       <c r="R37" t="n">
-        <v>6585917</v>
+        <v>6585875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B38" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R38" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427169</v>
+        <v>113426721</v>
       </c>
       <c r="B39" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561230</v>
+        <v>561083</v>
       </c>
       <c r="R39" t="n">
-        <v>6585884</v>
+        <v>6586092</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427186</v>
+        <v>113427121</v>
       </c>
       <c r="B40" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561348</v>
+        <v>561215</v>
       </c>
       <c r="R40" t="n">
-        <v>6585875</v>
+        <v>6585917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113426721</v>
+        <v>113427412</v>
       </c>
       <c r="B41" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561083</v>
+        <v>561202</v>
       </c>
       <c r="R41" t="n">
-        <v>6586092</v>
+        <v>6586118</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,7 +4901,7 @@
         <v>113427513</v>
       </c>
       <c r="B42" t="n">
-        <v>90077</v>
+        <v>90099</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90445</v>
+        <v>90467</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B46" t="n">
-        <v>91310</v>
+        <v>90695</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R46" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B47" t="n">
-        <v>90673</v>
+        <v>91332</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R47" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B34" t="n">
-        <v>90099</v>
+        <v>91367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,37 +4069,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R34" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,7 +4138,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4159,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B35" t="n">
-        <v>91363</v>
+        <v>90103</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,35 +4172,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R35" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,6 +4243,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113430772</v>
+        <v>113427186</v>
       </c>
       <c r="B36" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561351</v>
+        <v>561348</v>
       </c>
       <c r="R36" t="n">
-        <v>6586008</v>
+        <v>6585875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427186</v>
+        <v>113430772</v>
       </c>
       <c r="B37" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561348</v>
+        <v>561351</v>
       </c>
       <c r="R37" t="n">
-        <v>6585875</v>
+        <v>6586008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427169</v>
+        <v>113427513</v>
       </c>
       <c r="B38" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561230</v>
+        <v>561256</v>
       </c>
       <c r="R38" t="n">
-        <v>6585884</v>
+        <v>6585858</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113426721</v>
+        <v>113427169</v>
       </c>
       <c r="B39" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561083</v>
+        <v>561230</v>
       </c>
       <c r="R39" t="n">
-        <v>6586092</v>
+        <v>6585884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,7 +4689,7 @@
         <v>113427121</v>
       </c>
       <c r="B40" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>113427412</v>
       </c>
       <c r="B41" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427513</v>
+        <v>113426721</v>
       </c>
       <c r="B42" t="n">
-        <v>90099</v>
+        <v>90103</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561256</v>
+        <v>561083</v>
       </c>
       <c r="R42" t="n">
-        <v>6585858</v>
+        <v>6586092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
         <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>113444211</v>
       </c>
       <c r="B44" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90467</v>
+        <v>90471</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>113448130</v>
       </c>
       <c r="B46" t="n">
-        <v>90695</v>
+        <v>90699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>113415824</v>
       </c>
       <c r="B47" t="n">
-        <v>91332</v>
+        <v>91336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4262,7 +4262,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113427186</v>
+        <v>113427169</v>
       </c>
       <c r="B36" t="n">
         <v>90103</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561348</v>
+        <v>561230</v>
       </c>
       <c r="R36" t="n">
-        <v>6585875</v>
+        <v>6585884</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113430772</v>
+        <v>113426721</v>
       </c>
       <c r="B37" t="n">
         <v>90103</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561351</v>
+        <v>561083</v>
       </c>
       <c r="R37" t="n">
-        <v>6586008</v>
+        <v>6586092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427169</v>
+        <v>113430772</v>
       </c>
       <c r="B39" t="n">
         <v>90103</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561230</v>
+        <v>561351</v>
       </c>
       <c r="R39" t="n">
-        <v>6585884</v>
+        <v>6586008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113426721</v>
+        <v>113427186</v>
       </c>
       <c r="B42" t="n">
         <v>90103</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561083</v>
+        <v>561348</v>
       </c>
       <c r="R42" t="n">
-        <v>6586092</v>
+        <v>6585875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
         <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90471</v>
+        <v>90477</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>90699</v>
+        <v>91336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R46" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>91336</v>
+        <v>90699</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R47" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B34" t="n">
-        <v>91367</v>
+        <v>90109</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,35 +4069,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R34" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,6 +4140,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4156,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B35" t="n">
-        <v>90103</v>
+        <v>91373</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,37 +4175,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R35" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,7 +4244,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113427169</v>
+        <v>113430772</v>
       </c>
       <c r="B36" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561230</v>
+        <v>561351</v>
       </c>
       <c r="R36" t="n">
-        <v>6585884</v>
+        <v>6586008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
         <v>113426721</v>
       </c>
       <c r="B37" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427513</v>
+        <v>113427186</v>
       </c>
       <c r="B38" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561256</v>
+        <v>561348</v>
       </c>
       <c r="R38" t="n">
-        <v>6585858</v>
+        <v>6585875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113430772</v>
+        <v>113427121</v>
       </c>
       <c r="B39" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561351</v>
+        <v>561215</v>
       </c>
       <c r="R39" t="n">
-        <v>6586008</v>
+        <v>6585917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427121</v>
+        <v>113427412</v>
       </c>
       <c r="B40" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561215</v>
+        <v>561202</v>
       </c>
       <c r="R40" t="n">
-        <v>6585917</v>
+        <v>6586118</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B41" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R41" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427186</v>
+        <v>113427513</v>
       </c>
       <c r="B42" t="n">
-        <v>90103</v>
+        <v>90109</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561348</v>
+        <v>561256</v>
       </c>
       <c r="R42" t="n">
-        <v>6585875</v>
+        <v>6585858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5113,7 +5113,7 @@
         <v>113444211</v>
       </c>
       <c r="B44" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B46" t="n">
-        <v>91336</v>
+        <v>90705</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R46" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B47" t="n">
-        <v>90699</v>
+        <v>91342</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R47" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4262,7 +4262,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113430772</v>
+        <v>113427186</v>
       </c>
       <c r="B36" t="n">
         <v>90109</v>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561351</v>
+        <v>561348</v>
       </c>
       <c r="R36" t="n">
-        <v>6586008</v>
+        <v>6585875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113426721</v>
+        <v>113430772</v>
       </c>
       <c r="B37" t="n">
         <v>90109</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561083</v>
+        <v>561351</v>
       </c>
       <c r="R37" t="n">
-        <v>6586092</v>
+        <v>6586008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427186</v>
+        <v>113427513</v>
       </c>
       <c r="B38" t="n">
         <v>90109</v>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561348</v>
+        <v>561256</v>
       </c>
       <c r="R38" t="n">
-        <v>6585875</v>
+        <v>6585858</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427121</v>
+        <v>113426721</v>
       </c>
       <c r="B39" t="n">
         <v>90109</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561215</v>
+        <v>561083</v>
       </c>
       <c r="R39" t="n">
-        <v>6585917</v>
+        <v>6586092</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427513</v>
+        <v>113427121</v>
       </c>
       <c r="B42" t="n">
         <v>90109</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561256</v>
+        <v>561215</v>
       </c>
       <c r="R42" t="n">
-        <v>6585858</v>
+        <v>6585917</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4056,7 +4056,7 @@
         <v>113397423</v>
       </c>
       <c r="B34" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>113384128</v>
       </c>
       <c r="B35" t="n">
-        <v>91373</v>
+        <v>91380</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113427186</v>
+        <v>113426721</v>
       </c>
       <c r="B36" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561348</v>
+        <v>561083</v>
       </c>
       <c r="R36" t="n">
-        <v>6585875</v>
+        <v>6586092</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113430772</v>
+        <v>113427513</v>
       </c>
       <c r="B37" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561351</v>
+        <v>561256</v>
       </c>
       <c r="R37" t="n">
-        <v>6586008</v>
+        <v>6585858</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427513</v>
+        <v>113427186</v>
       </c>
       <c r="B38" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561256</v>
+        <v>561348</v>
       </c>
       <c r="R38" t="n">
-        <v>6585858</v>
+        <v>6585875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113426721</v>
+        <v>113427412</v>
       </c>
       <c r="B39" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561083</v>
+        <v>561202</v>
       </c>
       <c r="R39" t="n">
-        <v>6586092</v>
+        <v>6586118</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B40" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R40" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427169</v>
+        <v>113427121</v>
       </c>
       <c r="B41" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561230</v>
+        <v>561215</v>
       </c>
       <c r="R41" t="n">
-        <v>6585884</v>
+        <v>6585917</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427121</v>
+        <v>113430772</v>
       </c>
       <c r="B42" t="n">
-        <v>90109</v>
+        <v>90116</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561215</v>
+        <v>561351</v>
       </c>
       <c r="R42" t="n">
-        <v>6585917</v>
+        <v>6586008</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
         <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>113444211</v>
       </c>
       <c r="B44" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90477</v>
+        <v>90484</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>90705</v>
+        <v>91349</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R46" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>91342</v>
+        <v>90712</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R47" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B34" t="n">
-        <v>90116</v>
+        <v>91385</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,37 +4069,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R34" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,7 +4138,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4159,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B35" t="n">
-        <v>91380</v>
+        <v>90119</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,35 +4172,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R35" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,6 +4243,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>113426721</v>
       </c>
       <c r="B36" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427513</v>
+        <v>113427169</v>
       </c>
       <c r="B37" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561256</v>
+        <v>561230</v>
       </c>
       <c r="R37" t="n">
-        <v>6585858</v>
+        <v>6585884</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427186</v>
+        <v>113427513</v>
       </c>
       <c r="B38" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561348</v>
+        <v>561256</v>
       </c>
       <c r="R38" t="n">
-        <v>6585875</v>
+        <v>6585858</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,7 +4583,7 @@
         <v>113427412</v>
       </c>
       <c r="B39" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427169</v>
+        <v>113427186</v>
       </c>
       <c r="B40" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561230</v>
+        <v>561348</v>
       </c>
       <c r="R40" t="n">
-        <v>6585884</v>
+        <v>6585875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4795,7 +4795,7 @@
         <v>113427121</v>
       </c>
       <c r="B41" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>113430772</v>
       </c>
       <c r="B42" t="n">
-        <v>90116</v>
+        <v>90119</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>113444211</v>
       </c>
       <c r="B44" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90484</v>
+        <v>90489</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>91349</v>
+        <v>91354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>90712</v>
+        <v>90717</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B34" t="n">
-        <v>91385</v>
+        <v>90150</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,35 +4069,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R34" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,6 +4140,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4156,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B35" t="n">
-        <v>90119</v>
+        <v>91413</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4172,37 +4175,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R35" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,7 +4244,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>113426721</v>
       </c>
       <c r="B36" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427169</v>
+        <v>113427121</v>
       </c>
       <c r="B37" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561230</v>
+        <v>561215</v>
       </c>
       <c r="R37" t="n">
-        <v>6585884</v>
+        <v>6585917</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427513</v>
+        <v>113427412</v>
       </c>
       <c r="B38" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561256</v>
+        <v>561202</v>
       </c>
       <c r="R38" t="n">
-        <v>6585858</v>
+        <v>6586118</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427412</v>
+        <v>113427186</v>
       </c>
       <c r="B39" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561202</v>
+        <v>561348</v>
       </c>
       <c r="R39" t="n">
-        <v>6586118</v>
+        <v>6585875</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113427186</v>
+        <v>113430772</v>
       </c>
       <c r="B40" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561348</v>
+        <v>561351</v>
       </c>
       <c r="R40" t="n">
-        <v>6585875</v>
+        <v>6586008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427121</v>
+        <v>113427513</v>
       </c>
       <c r="B41" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561215</v>
+        <v>561256</v>
       </c>
       <c r="R41" t="n">
-        <v>6585917</v>
+        <v>6585858</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113430772</v>
+        <v>113427169</v>
       </c>
       <c r="B42" t="n">
-        <v>90119</v>
+        <v>90150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561351</v>
+        <v>561230</v>
       </c>
       <c r="R42" t="n">
-        <v>6586008</v>
+        <v>6585884</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5007,7 @@
         <v>113430910</v>
       </c>
       <c r="B43" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>113444211</v>
       </c>
       <c r="B44" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90489</v>
+        <v>90520</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B46" t="n">
-        <v>91354</v>
+        <v>90748</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R46" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B47" t="n">
-        <v>90717</v>
+        <v>91382</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R47" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113397423</v>
+        <v>113384128</v>
       </c>
       <c r="B34" t="n">
-        <v>90150</v>
+        <v>91413</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,37 +4069,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561345</v>
+        <v>561354</v>
       </c>
       <c r="R34" t="n">
-        <v>6586058</v>
+        <v>6586050</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,7 +4138,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4159,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113384128</v>
+        <v>113397423</v>
       </c>
       <c r="B35" t="n">
-        <v>91413</v>
+        <v>90151</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,35 +4172,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561354</v>
+        <v>561345</v>
       </c>
       <c r="R35" t="n">
-        <v>6586050</v>
+        <v>6586058</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,6 +4243,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113426721</v>
+        <v>113427186</v>
       </c>
       <c r="B36" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561083</v>
+        <v>561348</v>
       </c>
       <c r="R36" t="n">
-        <v>6586092</v>
+        <v>6585875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427121</v>
+        <v>113427169</v>
       </c>
       <c r="B37" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561215</v>
+        <v>561230</v>
       </c>
       <c r="R37" t="n">
-        <v>6585917</v>
+        <v>6585884</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113427412</v>
+        <v>113430772</v>
       </c>
       <c r="B38" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561202</v>
+        <v>561351</v>
       </c>
       <c r="R38" t="n">
-        <v>6586118</v>
+        <v>6586008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427186</v>
+        <v>113427513</v>
       </c>
       <c r="B39" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561348</v>
+        <v>561256</v>
       </c>
       <c r="R39" t="n">
-        <v>6585875</v>
+        <v>6585858</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113430772</v>
+        <v>113427121</v>
       </c>
       <c r="B40" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561351</v>
+        <v>561215</v>
       </c>
       <c r="R40" t="n">
-        <v>6586008</v>
+        <v>6585917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427513</v>
+        <v>113427412</v>
       </c>
       <c r="B41" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561256</v>
+        <v>561202</v>
       </c>
       <c r="R41" t="n">
-        <v>6585858</v>
+        <v>6586118</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113427169</v>
+        <v>113426721</v>
       </c>
       <c r="B42" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561230</v>
+        <v>561083</v>
       </c>
       <c r="R42" t="n">
-        <v>6585884</v>
+        <v>6586092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90520</v>
+        <v>90521</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>90748</v>
+        <v>91382</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R46" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>91382</v>
+        <v>90749</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R47" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -4262,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113427186</v>
+        <v>113427513</v>
       </c>
       <c r="B36" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561348</v>
+        <v>561256</v>
       </c>
       <c r="R36" t="n">
-        <v>6585875</v>
+        <v>6585858</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113427169</v>
+        <v>113427186</v>
       </c>
       <c r="B37" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561230</v>
+        <v>561348</v>
       </c>
       <c r="R37" t="n">
-        <v>6585884</v>
+        <v>6585875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113430772</v>
+        <v>113426721</v>
       </c>
       <c r="B38" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561351</v>
+        <v>561083</v>
       </c>
       <c r="R38" t="n">
-        <v>6586008</v>
+        <v>6586092</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113427513</v>
+        <v>113430772</v>
       </c>
       <c r="B39" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561256</v>
+        <v>561351</v>
       </c>
       <c r="R39" t="n">
-        <v>6585858</v>
+        <v>6586008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,7 +4689,7 @@
         <v>113427121</v>
       </c>
       <c r="B40" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113427412</v>
+        <v>113427169</v>
       </c>
       <c r="B41" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561202</v>
+        <v>561230</v>
       </c>
       <c r="R41" t="n">
-        <v>6586118</v>
+        <v>6585884</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113426721</v>
+        <v>113427412</v>
       </c>
       <c r="B42" t="n">
-        <v>90151</v>
+        <v>90155</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561083</v>
+        <v>561202</v>
       </c>
       <c r="R42" t="n">
-        <v>6586092</v>
+        <v>6586118</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
         <v>113444155</v>
       </c>
       <c r="B45" t="n">
-        <v>90521</v>
+        <v>90525</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>113415824</v>
       </c>
       <c r="B46" t="n">
-        <v>91382</v>
+        <v>91386</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>113448130</v>
       </c>
       <c r="B47" t="n">
-        <v>90749</v>
+        <v>90753</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113415824</v>
+        <v>113448130</v>
       </c>
       <c r="B46" t="n">
-        <v>91386</v>
+        <v>90753</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561276</v>
+        <v>561087</v>
       </c>
       <c r="R46" t="n">
-        <v>6586009</v>
+        <v>6586050</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113448130</v>
+        <v>113415824</v>
       </c>
       <c r="B47" t="n">
-        <v>90753</v>
+        <v>91386</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6031</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561087</v>
+        <v>561276</v>
       </c>
       <c r="R47" t="n">
-        <v>6586050</v>
+        <v>6586009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5532,6 +5532,112 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114990842</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90660</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>561303</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6586021</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5638,6 +5638,121 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>114991325</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>561306</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6586049</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -7879,10 +7879,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711368</v>
+        <v>117710892</v>
       </c>
       <c r="B69" t="n">
-        <v>8405</v>
+        <v>90521</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7891,36 +7891,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7928,10 +7922,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>561380</v>
+        <v>561248</v>
       </c>
       <c r="R69" t="n">
-        <v>6586040</v>
+        <v>6586028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7991,10 +7985,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117710892</v>
+        <v>117711368</v>
       </c>
       <c r="B70" t="n">
-        <v>90519</v>
+        <v>8405</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8003,30 +7997,36 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>561248</v>
+        <v>561380</v>
       </c>
       <c r="R70" t="n">
-        <v>6586028</v>
+        <v>6586040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8431,6 +8431,120 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120346271</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>561270</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6586026</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8545,6 +8545,218 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120497509</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>561346</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6586047</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120497365</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>561176</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6586111</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8757,6 +8757,960 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120540542</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>561137</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6585857</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120540124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>561176</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6585849</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120539811</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>561269</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6585846</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120540463</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>561177</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6585867</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120539987</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>561226</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6585846</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120540083</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>561212</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6585879</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120539933</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>561256</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6585828</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120539616</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>561261</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6585850</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120539455</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>561236</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6585866</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -8759,10 +8759,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120540542</v>
+        <v>120539455</v>
       </c>
       <c r="B77" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8775,21 +8775,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>561137</v>
+        <v>561236</v>
       </c>
       <c r="R77" t="n">
-        <v>6585857</v>
+        <v>6585866</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8865,10 +8865,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120540124</v>
+        <v>120539933</v>
       </c>
       <c r="B78" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8877,25 +8877,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>561176</v>
+        <v>561256</v>
       </c>
       <c r="R78" t="n">
-        <v>6585849</v>
+        <v>6585828</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8971,10 +8971,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120539811</v>
+        <v>120540124</v>
       </c>
       <c r="B79" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8987,21 +8987,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>561269</v>
+        <v>561176</v>
       </c>
       <c r="R79" t="n">
-        <v>6585846</v>
+        <v>6585849</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120540463</v>
+        <v>120539811</v>
       </c>
       <c r="B80" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>561177</v>
+        <v>561269</v>
       </c>
       <c r="R80" t="n">
-        <v>6585867</v>
+        <v>6585846</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9183,7 +9183,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120539987</v>
+        <v>120540083</v>
       </c>
       <c r="B81" t="n">
         <v>91881</v>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>561226</v>
+        <v>561212</v>
       </c>
       <c r="R81" t="n">
-        <v>6585846</v>
+        <v>6585879</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120540083</v>
+        <v>120539987</v>
       </c>
       <c r="B82" t="n">
         <v>91881</v>
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>561212</v>
+        <v>561226</v>
       </c>
       <c r="R82" t="n">
-        <v>6585879</v>
+        <v>6585846</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9395,10 +9395,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120539933</v>
+        <v>120539616</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9407,25 +9407,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>561256</v>
+        <v>561261</v>
       </c>
       <c r="R83" t="n">
-        <v>6585828</v>
+        <v>6585850</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9501,10 +9501,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120539616</v>
+        <v>120540542</v>
       </c>
       <c r="B84" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9517,21 +9517,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>561261</v>
+        <v>561137</v>
       </c>
       <c r="R84" t="n">
-        <v>6585850</v>
+        <v>6585857</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9607,7 +9607,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120539455</v>
+        <v>120540463</v>
       </c>
       <c r="B85" t="n">
         <v>91881</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>561236</v>
+        <v>561177</v>
       </c>
       <c r="R85" t="n">
-        <v>6585866</v>
+        <v>6585867</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10459,6 +10459,236 @@
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>123399306</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>561234</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6585839</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>123396997</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Malmtorp, Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>561274</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6585846</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10464,7 +10464,7 @@
         <v>123399306</v>
       </c>
       <c r="B93" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>123396997</v>
       </c>
       <c r="B94" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10461,10 +10461,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123399306</v>
+        <v>123396997</v>
       </c>
       <c r="B93" t="n">
-        <v>57632</v>
+        <v>57634</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10499,23 +10499,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Malmtorp, Srm</t>
+          <t>Malmtorp, Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561234</v>
+        <v>561274</v>
       </c>
       <c r="R93" t="n">
-        <v>6585839</v>
+        <v>6585846</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10542,9 +10542,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10571,10 +10581,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123396997</v>
+        <v>123399306</v>
       </c>
       <c r="B94" t="n">
-        <v>57634</v>
+        <v>57632</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10587,21 +10597,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10609,23 +10619,23 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Malmtorp, Malmtorp, Srm</t>
+          <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>561274</v>
+        <v>561234</v>
       </c>
       <c r="R94" t="n">
-        <v>6585846</v>
+        <v>6585839</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10652,19 +10662,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10464,7 +10464,7 @@
         <v>123396997</v>
       </c>
       <c r="B93" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>123399306</v>
       </c>
       <c r="B94" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10461,10 +10461,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123396997</v>
+        <v>123399306</v>
       </c>
       <c r="B93" t="n">
-        <v>57640</v>
+        <v>57641</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10499,23 +10499,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Malmtorp, Malmtorp, Srm</t>
+          <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561274</v>
+        <v>561234</v>
       </c>
       <c r="R93" t="n">
-        <v>6585846</v>
+        <v>6585839</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10542,19 +10542,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10581,10 +10571,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123399306</v>
+        <v>123396997</v>
       </c>
       <c r="B94" t="n">
-        <v>57638</v>
+        <v>57643</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10597,21 +10587,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,23 +10609,23 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Malmtorp, Srm</t>
+          <t>Malmtorp, Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>561234</v>
+        <v>561274</v>
       </c>
       <c r="R94" t="n">
-        <v>6585839</v>
+        <v>6585846</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10662,9 +10652,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10461,10 +10461,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123399306</v>
+        <v>123396997</v>
       </c>
       <c r="B93" t="n">
-        <v>57641</v>
+        <v>57644</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10499,23 +10499,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Malmtorp, Srm</t>
+          <t>Malmtorp, Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561234</v>
+        <v>561274</v>
       </c>
       <c r="R93" t="n">
-        <v>6585839</v>
+        <v>6585846</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10542,9 +10542,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10571,10 +10581,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123396997</v>
+        <v>123399306</v>
       </c>
       <c r="B94" t="n">
-        <v>57643</v>
+        <v>57642</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10587,21 +10597,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10609,23 +10619,23 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Malmtorp, Malmtorp, Srm</t>
+          <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>561274</v>
+        <v>561234</v>
       </c>
       <c r="R94" t="n">
-        <v>6585846</v>
+        <v>6585839</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10652,19 +10662,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10461,10 +10461,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123396997</v>
+        <v>123399306</v>
       </c>
       <c r="B93" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10499,23 +10499,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Malmtorp, Malmtorp, Srm</t>
+          <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561274</v>
+        <v>561234</v>
       </c>
       <c r="R93" t="n">
-        <v>6585846</v>
+        <v>6585839</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10542,19 +10542,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10581,10 +10571,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123399306</v>
+        <v>123396997</v>
       </c>
       <c r="B94" t="n">
-        <v>57642</v>
+        <v>57644</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10597,21 +10587,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10619,23 +10609,23 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Malmtorp, Srm</t>
+          <t>Malmtorp, Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>561234</v>
+        <v>561274</v>
       </c>
       <c r="R94" t="n">
-        <v>6585839</v>
+        <v>6585846</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10662,9 +10652,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10461,10 +10461,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123399306</v>
+        <v>123396997</v>
       </c>
       <c r="B93" t="n">
-        <v>57642</v>
+        <v>57644</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10477,21 +10477,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10499,23 +10499,23 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Malmtorp, Srm</t>
+          <t>Malmtorp, Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561234</v>
+        <v>561274</v>
       </c>
       <c r="R93" t="n">
-        <v>6585839</v>
+        <v>6585846</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10542,9 +10542,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10571,10 +10581,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123396997</v>
+        <v>123399306</v>
       </c>
       <c r="B94" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10587,21 +10597,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10609,23 +10619,23 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Malmtorp, Malmtorp, Srm</t>
+          <t>Malmtorp, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>561274</v>
+        <v>561234</v>
       </c>
       <c r="R94" t="n">
-        <v>6585846</v>
+        <v>6585839</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10652,19 +10662,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10689,6 +10689,111 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126125483</v>
+      </c>
+      <c r="B95" t="n">
+        <v>58130</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>561265</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6585982</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10694,7 +10694,7 @@
         <v>126125483</v>
       </c>
       <c r="B95" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10694,7 +10694,7 @@
         <v>126125483</v>
       </c>
       <c r="B95" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -10694,7 +10694,7 @@
         <v>126125483</v>
       </c>
       <c r="B95" t="n">
-        <v>58135</v>
+        <v>58138</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 50121-2023 artfynd.xlsx
+++ b/artfynd/A 50121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10799,7 +10799,7 @@
         <v>127064166</v>
       </c>
       <c r="B96" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>127064419</v>
       </c>
       <c r="B97" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>127065207</v>
       </c>
       <c r="B98" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11140,6 +11140,588 @@
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127298229</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>561390</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6585904</v>
+      </c>
+      <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>2 st. blomstjälkar.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127295680</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91339</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>561335</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6586010</v>
+      </c>
+      <c r="S100" t="n">
+        <v>8</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127294770</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>561316</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6586026</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>27 st blomstjälkar.</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127296017</v>
+      </c>
+      <c r="B102" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>561324</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6586014</v>
+      </c>
+      <c r="S102" t="n">
+        <v>8</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127297786</v>
+      </c>
+      <c r="B103" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Malmtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>561403</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6585888</v>
+      </c>
+      <c r="S103" t="n">
+        <v>8</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
